--- a/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_27_4_mar.xlsx
+++ b/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_27_4_mar.xlsx
@@ -2907,7 +2907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{37d03cbd-1952-48bd-bf06-2c65b3bac071}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{f48502e6-bb31-4e0b-847c-2b671ba4cb08}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr codeName="Лист1">
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -7990,7 +7990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{d121660f-a935-423b-ab13-e90365736b0d}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{28602433-b8ae-443a-8a35-0cdf78f65b2c}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
